--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2465,6 +2465,1578 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129503586</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91514</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skrikemosse, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>401504</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6364617</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ambjörnarp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129458846</v>
+      </c>
+      <c r="B19" t="n">
+        <v>75161</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>401650</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6364547</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ambjörnarp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129462173</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91514</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>401582</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6364517</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ambjörnarp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129503618</v>
+      </c>
+      <c r="B21" t="n">
+        <v>83004</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>308</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skrikemosse, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>401544</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6364485</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ambjörnarp</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129503578</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97006</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skrikemosse, Vg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>401510</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6364570</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ambjörnarp</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129503567</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91514</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skrikemosse, Vg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>401505</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6364565</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ambjörnarp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129465035</v>
+      </c>
+      <c r="B24" t="n">
+        <v>75161</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>401491</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6364685</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ambjörnarp</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129460715</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97006</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>401576</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6364499</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ambjörnarp</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129464861</v>
+      </c>
+      <c r="B26" t="n">
+        <v>83004</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>308</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>401498</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6364606</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ambjörnarp</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129503672</v>
+      </c>
+      <c r="B27" t="n">
+        <v>95960</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skrikemosse, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>401640</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6364547</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ambjörnarp</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129504302</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97006</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skrikemosse, Vg</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>401534</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6364584</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ambjörnarp</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129461207</v>
+      </c>
+      <c r="B29" t="n">
+        <v>83004</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>308</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tranemo, Tranemo kommun, Götaland, Västra Götalands län, Tranemo, Tranemo kommun, Götaland, Västra Götalands län, Vg</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>401543</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6364475</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ambjörnarp</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129464928</v>
+      </c>
+      <c r="B30" t="n">
+        <v>75161</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>401488</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6364661</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ambjörnarp</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129462141</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97006</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>401582</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6364517</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ambjörnarp</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129461099</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91514</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tranemo, Tranemo kommun, Götaland, Västra Götalands län, Tranemo, Tranemo kommun, Götaland, Västra Götalands län, Vg</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>401543</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6364475</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ambjörnarp</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -2675,48 +2675,51 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129462173</v>
+        <v>129503618</v>
       </c>
       <c r="B20" t="n">
-        <v>91514</v>
+        <v>83004</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rödebäcken, Rödebäcken, Vg</t>
+          <t>Skrikemosse, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401582</v>
+        <v>401544</v>
       </c>
       <c r="R20" t="n">
-        <v>6364517</v>
+        <v>6364485</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,90 +2746,78 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129503618</v>
+        <v>129462173</v>
       </c>
       <c r="B21" t="n">
-        <v>83004</v>
+        <v>91514</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skrikemosse, Vg</t>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401544</v>
+        <v>401582</v>
       </c>
       <c r="R21" t="n">
-        <v>6364485</v>
+        <v>6364517</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,30 +2844,39 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129503672</v>
+        <v>129504302</v>
       </c>
       <c r="B27" t="n">
-        <v>95960</v>
+        <v>97006</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401640</v>
+        <v>401534</v>
       </c>
       <c r="R27" t="n">
-        <v>6364547</v>
+        <v>6364584</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129504302</v>
+        <v>129503672</v>
       </c>
       <c r="B28" t="n">
-        <v>97006</v>
+        <v>95960</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>401534</v>
+        <v>401640</v>
       </c>
       <c r="R28" t="n">
-        <v>6364584</v>
+        <v>6364547</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>

--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -2470,7 +2470,7 @@
         <v>129503586</v>
       </c>
       <c r="B18" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,51 +2675,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129503618</v>
+        <v>129462173</v>
       </c>
       <c r="B20" t="n">
-        <v>83004</v>
+        <v>91517</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skrikemosse, Vg</t>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401544</v>
+        <v>401582</v>
       </c>
       <c r="R20" t="n">
-        <v>6364485</v>
+        <v>6364517</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2746,78 +2743,90 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129462173</v>
+        <v>129503618</v>
       </c>
       <c r="B21" t="n">
-        <v>91514</v>
+        <v>83004</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rödebäcken, Rödebäcken, Vg</t>
+          <t>Skrikemosse, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401582</v>
+        <v>401544</v>
       </c>
       <c r="R21" t="n">
-        <v>6364517</v>
+        <v>6364485</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2844,39 +2853,30 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2886,7 +2886,7 @@
         <v>129503578</v>
       </c>
       <c r="B22" t="n">
-        <v>97006</v>
+        <v>97009</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>129503567</v>
       </c>
       <c r="B23" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129460715</v>
       </c>
       <c r="B25" t="n">
-        <v>97006</v>
+        <v>97009</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129504302</v>
+        <v>129503672</v>
       </c>
       <c r="B27" t="n">
-        <v>97006</v>
+        <v>95963</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401534</v>
+        <v>401640</v>
       </c>
       <c r="R27" t="n">
-        <v>6364584</v>
+        <v>6364547</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129503672</v>
+        <v>129504302</v>
       </c>
       <c r="B28" t="n">
-        <v>95960</v>
+        <v>97009</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>401640</v>
+        <v>401534</v>
       </c>
       <c r="R28" t="n">
-        <v>6364547</v>
+        <v>6364584</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3828,7 +3828,7 @@
         <v>129462141</v>
       </c>
       <c r="B31" t="n">
-        <v>97006</v>
+        <v>97009</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>129461099</v>
       </c>
       <c r="B32" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -2675,48 +2675,51 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129462173</v>
+        <v>129503618</v>
       </c>
       <c r="B20" t="n">
-        <v>91517</v>
+        <v>83004</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rödebäcken, Rödebäcken, Vg</t>
+          <t>Skrikemosse, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401582</v>
+        <v>401544</v>
       </c>
       <c r="R20" t="n">
-        <v>6364517</v>
+        <v>6364485</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,90 +2746,78 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129503618</v>
+        <v>129462173</v>
       </c>
       <c r="B21" t="n">
-        <v>83004</v>
+        <v>91517</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skrikemosse, Vg</t>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401544</v>
+        <v>401582</v>
       </c>
       <c r="R21" t="n">
-        <v>6364485</v>
+        <v>6364517</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,30 +2844,39 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129503672</v>
+        <v>129504302</v>
       </c>
       <c r="B27" t="n">
-        <v>95963</v>
+        <v>97009</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401640</v>
+        <v>401534</v>
       </c>
       <c r="R27" t="n">
-        <v>6364547</v>
+        <v>6364584</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129504302</v>
+        <v>129503672</v>
       </c>
       <c r="B28" t="n">
-        <v>97009</v>
+        <v>95963</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>401534</v>
+        <v>401640</v>
       </c>
       <c r="R28" t="n">
-        <v>6364584</v>
+        <v>6364547</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>

--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -2675,51 +2675,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129503618</v>
+        <v>129462173</v>
       </c>
       <c r="B20" t="n">
-        <v>83004</v>
+        <v>91517</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skrikemosse, Vg</t>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401544</v>
+        <v>401582</v>
       </c>
       <c r="R20" t="n">
-        <v>6364485</v>
+        <v>6364517</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2746,78 +2743,90 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129462173</v>
+        <v>129503618</v>
       </c>
       <c r="B21" t="n">
-        <v>91517</v>
+        <v>83004</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rödebäcken, Rödebäcken, Vg</t>
+          <t>Skrikemosse, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401582</v>
+        <v>401544</v>
       </c>
       <c r="R21" t="n">
-        <v>6364517</v>
+        <v>6364485</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2844,39 +2853,30 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -2675,48 +2675,51 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129462173</v>
+        <v>129503618</v>
       </c>
       <c r="B20" t="n">
-        <v>91517</v>
+        <v>83004</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rödebäcken, Rödebäcken, Vg</t>
+          <t>Skrikemosse, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401582</v>
+        <v>401544</v>
       </c>
       <c r="R20" t="n">
-        <v>6364517</v>
+        <v>6364485</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,90 +2746,78 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129503618</v>
+        <v>129462173</v>
       </c>
       <c r="B21" t="n">
-        <v>83004</v>
+        <v>91517</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skrikemosse, Vg</t>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401544</v>
+        <v>401582</v>
       </c>
       <c r="R21" t="n">
-        <v>6364485</v>
+        <v>6364517</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,30 +2844,39 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -2470,7 +2470,7 @@
         <v>129503586</v>
       </c>
       <c r="B18" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>129458846</v>
       </c>
       <c r="B19" t="n">
-        <v>75161</v>
+        <v>75182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>129462173</v>
       </c>
       <c r="B20" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>129503618</v>
       </c>
       <c r="B21" t="n">
-        <v>83004</v>
+        <v>83031</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>129503578</v>
       </c>
       <c r="B22" t="n">
-        <v>97009</v>
+        <v>97038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>129503567</v>
       </c>
       <c r="B23" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129465035</v>
       </c>
       <c r="B24" t="n">
-        <v>75161</v>
+        <v>75182</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129460715</v>
       </c>
       <c r="B25" t="n">
-        <v>97009</v>
+        <v>97038</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>129464861</v>
       </c>
       <c r="B26" t="n">
-        <v>83004</v>
+        <v>83031</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129504302</v>
+        <v>129503672</v>
       </c>
       <c r="B27" t="n">
-        <v>97009</v>
+        <v>95992</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401534</v>
+        <v>401640</v>
       </c>
       <c r="R27" t="n">
-        <v>6364584</v>
+        <v>6364547</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129503672</v>
+        <v>129504302</v>
       </c>
       <c r="B28" t="n">
-        <v>95963</v>
+        <v>97038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>401640</v>
+        <v>401534</v>
       </c>
       <c r="R28" t="n">
-        <v>6364547</v>
+        <v>6364584</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3614,7 +3614,7 @@
         <v>129461207</v>
       </c>
       <c r="B29" t="n">
-        <v>83004</v>
+        <v>83031</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>129464928</v>
       </c>
       <c r="B30" t="n">
-        <v>75161</v>
+        <v>75182</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>129462141</v>
       </c>
       <c r="B31" t="n">
-        <v>97009</v>
+        <v>97038</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>129461099</v>
       </c>
       <c r="B32" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129503672</v>
+        <v>129504302</v>
       </c>
       <c r="B27" t="n">
-        <v>95992</v>
+        <v>97038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401640</v>
+        <v>401534</v>
       </c>
       <c r="R27" t="n">
-        <v>6364547</v>
+        <v>6364584</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129504302</v>
+        <v>129503672</v>
       </c>
       <c r="B28" t="n">
-        <v>97038</v>
+        <v>95992</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>401534</v>
+        <v>401640</v>
       </c>
       <c r="R28" t="n">
-        <v>6364584</v>
+        <v>6364547</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>

--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -2470,7 +2470,7 @@
         <v>129503586</v>
       </c>
       <c r="B18" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>129458846</v>
       </c>
       <c r="B19" t="n">
-        <v>75182</v>
+        <v>75187</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2675,48 +2675,51 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129462173</v>
+        <v>129503618</v>
       </c>
       <c r="B20" t="n">
-        <v>91545</v>
+        <v>83036</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rödebäcken, Rödebäcken, Vg</t>
+          <t>Skrikemosse, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401582</v>
+        <v>401544</v>
       </c>
       <c r="R20" t="n">
-        <v>6364517</v>
+        <v>6364485</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,90 +2746,78 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129503618</v>
+        <v>129462173</v>
       </c>
       <c r="B21" t="n">
-        <v>83031</v>
+        <v>91551</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skrikemosse, Vg</t>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401544</v>
+        <v>401582</v>
       </c>
       <c r="R21" t="n">
-        <v>6364485</v>
+        <v>6364517</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,30 +2844,39 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2886,7 +2886,7 @@
         <v>129503578</v>
       </c>
       <c r="B22" t="n">
-        <v>97038</v>
+        <v>97050</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>129503567</v>
       </c>
       <c r="B23" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129465035</v>
       </c>
       <c r="B24" t="n">
-        <v>75182</v>
+        <v>75187</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129460715</v>
       </c>
       <c r="B25" t="n">
-        <v>97038</v>
+        <v>97050</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>129464861</v>
       </c>
       <c r="B26" t="n">
-        <v>83031</v>
+        <v>83036</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>129504302</v>
       </c>
       <c r="B27" t="n">
-        <v>97038</v>
+        <v>97050</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>129503672</v>
       </c>
       <c r="B28" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>129461207</v>
       </c>
       <c r="B29" t="n">
-        <v>83031</v>
+        <v>83036</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>129464928</v>
       </c>
       <c r="B30" t="n">
-        <v>75182</v>
+        <v>75187</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>129462141</v>
       </c>
       <c r="B31" t="n">
-        <v>97038</v>
+        <v>97050</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>129461099</v>
       </c>
       <c r="B32" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -2470,7 +2470,7 @@
         <v>129503586</v>
       </c>
       <c r="B18" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>129458846</v>
       </c>
       <c r="B19" t="n">
-        <v>75187</v>
+        <v>75188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2675,51 +2675,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129503618</v>
+        <v>129462173</v>
       </c>
       <c r="B20" t="n">
-        <v>83036</v>
+        <v>91552</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skrikemosse, Vg</t>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401544</v>
+        <v>401582</v>
       </c>
       <c r="R20" t="n">
-        <v>6364485</v>
+        <v>6364517</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2746,78 +2743,90 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129462173</v>
+        <v>129503618</v>
       </c>
       <c r="B21" t="n">
-        <v>91551</v>
+        <v>83037</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rödebäcken, Rödebäcken, Vg</t>
+          <t>Skrikemosse, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401582</v>
+        <v>401544</v>
       </c>
       <c r="R21" t="n">
-        <v>6364517</v>
+        <v>6364485</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2844,39 +2853,30 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2886,7 +2886,7 @@
         <v>129503578</v>
       </c>
       <c r="B22" t="n">
-        <v>97050</v>
+        <v>97051</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>129503567</v>
       </c>
       <c r="B23" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129465035</v>
       </c>
       <c r="B24" t="n">
-        <v>75187</v>
+        <v>75188</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129460715</v>
       </c>
       <c r="B25" t="n">
-        <v>97050</v>
+        <v>97051</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>129464861</v>
       </c>
       <c r="B26" t="n">
-        <v>83036</v>
+        <v>83037</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129504302</v>
+        <v>129503672</v>
       </c>
       <c r="B27" t="n">
-        <v>97050</v>
+        <v>96005</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401534</v>
+        <v>401640</v>
       </c>
       <c r="R27" t="n">
-        <v>6364584</v>
+        <v>6364547</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129503672</v>
+        <v>129504302</v>
       </c>
       <c r="B28" t="n">
-        <v>96004</v>
+        <v>97051</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>401640</v>
+        <v>401534</v>
       </c>
       <c r="R28" t="n">
-        <v>6364547</v>
+        <v>6364584</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3614,7 +3614,7 @@
         <v>129461207</v>
       </c>
       <c r="B29" t="n">
-        <v>83036</v>
+        <v>83037</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>129464928</v>
       </c>
       <c r="B30" t="n">
-        <v>75187</v>
+        <v>75188</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>129462141</v>
       </c>
       <c r="B31" t="n">
-        <v>97050</v>
+        <v>97051</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>129461099</v>
       </c>
       <c r="B32" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -2675,48 +2675,51 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129462173</v>
+        <v>129503618</v>
       </c>
       <c r="B20" t="n">
-        <v>91552</v>
+        <v>83037</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rödebäcken, Rödebäcken, Vg</t>
+          <t>Skrikemosse, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401582</v>
+        <v>401544</v>
       </c>
       <c r="R20" t="n">
-        <v>6364517</v>
+        <v>6364485</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,90 +2746,78 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129503618</v>
+        <v>129462173</v>
       </c>
       <c r="B21" t="n">
-        <v>83037</v>
+        <v>91552</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skrikemosse, Vg</t>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401544</v>
+        <v>401582</v>
       </c>
       <c r="R21" t="n">
-        <v>6364485</v>
+        <v>6364517</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,30 +2844,39 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -2470,7 +2470,7 @@
         <v>129503586</v>
       </c>
       <c r="B18" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>129458846</v>
       </c>
       <c r="B19" t="n">
-        <v>75188</v>
+        <v>75193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>129503618</v>
       </c>
       <c r="B20" t="n">
-        <v>83037</v>
+        <v>83042</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>129462173</v>
       </c>
       <c r="B21" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>129503578</v>
       </c>
       <c r="B22" t="n">
-        <v>97051</v>
+        <v>97056</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>129503567</v>
       </c>
       <c r="B23" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129465035</v>
       </c>
       <c r="B24" t="n">
-        <v>75188</v>
+        <v>75193</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129460715</v>
       </c>
       <c r="B25" t="n">
-        <v>97051</v>
+        <v>97056</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>129464861</v>
       </c>
       <c r="B26" t="n">
-        <v>83037</v>
+        <v>83042</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129503672</v>
+        <v>129504302</v>
       </c>
       <c r="B27" t="n">
-        <v>96005</v>
+        <v>97056</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401640</v>
+        <v>401534</v>
       </c>
       <c r="R27" t="n">
-        <v>6364547</v>
+        <v>6364584</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129504302</v>
+        <v>129503672</v>
       </c>
       <c r="B28" t="n">
-        <v>97051</v>
+        <v>96010</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>401534</v>
+        <v>401640</v>
       </c>
       <c r="R28" t="n">
-        <v>6364584</v>
+        <v>6364547</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3614,7 +3614,7 @@
         <v>129461207</v>
       </c>
       <c r="B29" t="n">
-        <v>83037</v>
+        <v>83042</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>129464928</v>
       </c>
       <c r="B30" t="n">
-        <v>75188</v>
+        <v>75193</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>129462141</v>
       </c>
       <c r="B31" t="n">
-        <v>97051</v>
+        <v>97056</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>129461099</v>
       </c>
       <c r="B32" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -2675,51 +2675,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129503618</v>
+        <v>129462173</v>
       </c>
       <c r="B20" t="n">
-        <v>83042</v>
+        <v>91557</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skrikemosse, Vg</t>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401544</v>
+        <v>401582</v>
       </c>
       <c r="R20" t="n">
-        <v>6364485</v>
+        <v>6364517</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2746,78 +2743,90 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129462173</v>
+        <v>129503618</v>
       </c>
       <c r="B21" t="n">
-        <v>91557</v>
+        <v>83042</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rödebäcken, Rödebäcken, Vg</t>
+          <t>Skrikemosse, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401582</v>
+        <v>401544</v>
       </c>
       <c r="R21" t="n">
-        <v>6364517</v>
+        <v>6364485</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2844,39 +2853,30 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129504302</v>
+        <v>129503672</v>
       </c>
       <c r="B27" t="n">
-        <v>97056</v>
+        <v>96010</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401534</v>
+        <v>401640</v>
       </c>
       <c r="R27" t="n">
-        <v>6364584</v>
+        <v>6364547</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129503672</v>
+        <v>129504302</v>
       </c>
       <c r="B28" t="n">
-        <v>96010</v>
+        <v>97056</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>401640</v>
+        <v>401534</v>
       </c>
       <c r="R28" t="n">
-        <v>6364547</v>
+        <v>6364584</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>

--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -2470,7 +2470,7 @@
         <v>129503586</v>
       </c>
       <c r="B18" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>129462173</v>
       </c>
       <c r="B20" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>129503578</v>
       </c>
       <c r="B22" t="n">
-        <v>97056</v>
+        <v>97060</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>129503567</v>
       </c>
       <c r="B23" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129460715</v>
       </c>
       <c r="B25" t="n">
-        <v>97056</v>
+        <v>97060</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129503672</v>
+        <v>129504302</v>
       </c>
       <c r="B27" t="n">
-        <v>96010</v>
+        <v>97060</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401640</v>
+        <v>401534</v>
       </c>
       <c r="R27" t="n">
-        <v>6364547</v>
+        <v>6364584</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129504302</v>
+        <v>129503672</v>
       </c>
       <c r="B28" t="n">
-        <v>97056</v>
+        <v>96014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>401534</v>
+        <v>401640</v>
       </c>
       <c r="R28" t="n">
-        <v>6364584</v>
+        <v>6364547</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3828,7 +3828,7 @@
         <v>129462141</v>
       </c>
       <c r="B31" t="n">
-        <v>97056</v>
+        <v>97060</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>129461099</v>
       </c>
       <c r="B32" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -2470,7 +2470,7 @@
         <v>129503586</v>
       </c>
       <c r="B18" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,48 +2675,51 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129462173</v>
+        <v>129503618</v>
       </c>
       <c r="B20" t="n">
-        <v>91561</v>
+        <v>83044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rödebäcken, Rödebäcken, Vg</t>
+          <t>Skrikemosse, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401582</v>
+        <v>401544</v>
       </c>
       <c r="R20" t="n">
-        <v>6364517</v>
+        <v>6364485</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,90 +2746,78 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129503618</v>
+        <v>129462173</v>
       </c>
       <c r="B21" t="n">
-        <v>83042</v>
+        <v>91563</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skrikemosse, Vg</t>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401544</v>
+        <v>401582</v>
       </c>
       <c r="R21" t="n">
-        <v>6364485</v>
+        <v>6364517</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,30 +2844,39 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2886,7 +2886,7 @@
         <v>129503578</v>
       </c>
       <c r="B22" t="n">
-        <v>97060</v>
+        <v>97062</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>129503567</v>
       </c>
       <c r="B23" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129460715</v>
       </c>
       <c r="B25" t="n">
-        <v>97060</v>
+        <v>97062</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>129464861</v>
       </c>
       <c r="B26" t="n">
-        <v>83042</v>
+        <v>83044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>129504302</v>
       </c>
       <c r="B27" t="n">
-        <v>97060</v>
+        <v>97062</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>129503672</v>
       </c>
       <c r="B28" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>129461207</v>
       </c>
       <c r="B29" t="n">
-        <v>83042</v>
+        <v>83044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>129462141</v>
       </c>
       <c r="B31" t="n">
-        <v>97060</v>
+        <v>97062</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>129461099</v>
       </c>
       <c r="B32" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -2675,51 +2675,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129503618</v>
+        <v>129462173</v>
       </c>
       <c r="B20" t="n">
-        <v>83044</v>
+        <v>91563</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skrikemosse, Vg</t>
+          <t>Rödebäcken, Rödebäcken, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401544</v>
+        <v>401582</v>
       </c>
       <c r="R20" t="n">
-        <v>6364485</v>
+        <v>6364517</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2746,78 +2743,90 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129462173</v>
+        <v>129503618</v>
       </c>
       <c r="B21" t="n">
-        <v>91563</v>
+        <v>83044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rödebäcken, Rödebäcken, Vg</t>
+          <t>Skrikemosse, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401582</v>
+        <v>401544</v>
       </c>
       <c r="R21" t="n">
-        <v>6364517</v>
+        <v>6364485</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2844,39 +2853,30 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 48663-2025 artfynd.xlsx
+++ b/artfynd/A 48663-2025 artfynd.xlsx
@@ -2886,7 +2886,7 @@
         <v>129503578</v>
       </c>
       <c r="B22" t="n">
-        <v>97062</v>
+        <v>97072</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129460715</v>
       </c>
       <c r="B25" t="n">
-        <v>97062</v>
+        <v>97072</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>129504302</v>
       </c>
       <c r="B27" t="n">
-        <v>97062</v>
+        <v>97072</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>129503672</v>
       </c>
       <c r="B28" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>129462141</v>
       </c>
       <c r="B31" t="n">
-        <v>97062</v>
+        <v>97072</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
